--- a/resources/one-person-ai-business/files/opab-adv-leverage-scoreboard.xlsx
+++ b/resources/one-person-ai-business/files/opab-adv-leverage-scoreboard.xlsx
@@ -17,10 +17,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="&quot;£&quot;#,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,11 +67,6 @@
       <color rgb="000C2733"/>
       <sz val="12"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="005A5A5A"/>
-    </font>
-    <font/>
   </fonts>
   <fills count="3">
     <fill>
@@ -98,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -129,8 +124,6 @@
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -496,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -515,11 +508,10 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Edit the yellow cells, in YOUR currency. Ratio = net revenue ÷ RECURRING hours only. Free from ePORTS — eports.global/one-person-ai-business</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>Edit the yellow cells, in YOUR currency. Ratio = net revenue ÷ RECURRING hours only. Net revenue excludes any sales tax you collect (that passes through to the state). Free from ePORTS — eports.global/one-person-ai-business</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -545,7 +537,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>£ / hour</t>
+          <t>$ / hour</t>
         </is>
       </c>
     </row>
@@ -586,7 +578,7 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Bespoke / one-to-one</t>
+          <t>Custom / one-to-one</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
@@ -620,7 +612,7 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Leveraged core (memo: rows 1–2, excl. bespoke)</t>
+          <t>Leveraged core (memo: rows 1–2, excl. custom)</t>
         </is>
       </c>
       <c r="B10" s="11">
@@ -658,18 +650,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>With the defaults: core £4,500/25 = £180; blended £6,000/40 = £150 — the bespoke line</t>
+          <t>With the defaults: core $4,500/25 = $180; blended $6,000/40 = $150 — the custom line</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>drags the average down. Any activity below the blended £/hour is a drag (see ch8).</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>drags the average down. Any activity below the blended $/hour is a drag (see ch8).</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
@@ -695,7 +686,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Ratio £/hr</t>
+          <t>Ratio $/hr</t>
         </is>
       </c>
     </row>
@@ -903,7 +894,6 @@
         <v/>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
@@ -918,7 +908,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
@@ -932,10 +921,6 @@
           <t>ePORTS — your ecom source. eports.global.</t>
         </is>
       </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="15" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resources/one-person-ai-business/files/opab-adv-leverage-scoreboard.xlsx
+++ b/resources/one-person-ai-business/files/opab-adv-leverage-scoreboard.xlsx
@@ -918,7 +918,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
+          <t>ePORTS — your ecom source (eports.global)</t>
         </is>
       </c>
     </row>
